--- a/Analysis-Config.xlsx
+++ b/Analysis-Config.xlsx
@@ -521,8 +521,6 @@
           <t>1=Weiblich;2=Männlich;3=Divers</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -533,7 +531,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,7 +548,6 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>18</t>
@@ -599,8 +595,6 @@
           <t>1=Hauptschule;2=Realschule;3=Abitur;4=Universität</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -611,7 +605,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -701,7 +694,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -744,7 +736,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -767,8 +758,6 @@
           <t>1=Ausgewählt</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -801,7 +790,6 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>1</t>
@@ -897,7 +885,6 @@
           <t>chi_square</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -974,7 +961,6 @@
           <t>mann_whitney</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1022,6 +1008,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1050,6 +1037,11 @@
           <t>filter</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cluster_variable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1072,7 +1064,7 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1100,6 +1092,7 @@
           <t>SD02 &gt;= 18</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1122,7 +1115,7 @@
           <t>t_test</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1150,6 +1143,7 @@
           <t>!is.na(zufriedenheit_index)</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1175,6 +1169,11 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>SD01 == 1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>attribute_2</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1257,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1303,7 +1301,6 @@
           <t>ZF01[other]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>10</t>
@@ -1314,7 +1311,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
